--- a/artfynd/A 62250-2025 artfynd.xlsx
+++ b/artfynd/A 62250-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130078193</v>
       </c>
       <c r="B3" t="n">
-        <v>79181</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62250-2025 artfynd.xlsx
+++ b/artfynd/A 62250-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126355436</v>
+        <v>126355438</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394255</v>
+        <v>394239</v>
       </c>
       <c r="R2" t="n">
-        <v>6730369</v>
+        <v>6730448</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130078193</v>
+        <v>126355437</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394200</v>
+        <v>394267</v>
       </c>
       <c r="R3" t="n">
-        <v>6730429</v>
+        <v>6730352</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,6 +866,394 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126355436</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Knölarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>394255</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6730369</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130078193</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Knölarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>394200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6730429</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126355439</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Knölarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>394239</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6730451</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126355435</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knölarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>394280</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6730388</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62250-2025 artfynd.xlsx
+++ b/artfynd/A 62250-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355438</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355437</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355436</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130078193</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355439</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126355435</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>